--- a/test/taxaudit.xlsx
+++ b/test/taxaudit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196DDCA0-A351-4C04-B96B-9782D5FFCBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54E9F6E-3E43-445D-A795-AFC5499056CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{BFEA6EE1-7901-49E1-AA3E-165960DD2B10}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>month</t>
   </si>
@@ -443,12 +443,6 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
